--- a/Assets/Data/Dungeon0021.xlsx
+++ b/Assets/Data/Dungeon0021.xlsx
@@ -55,7 +55,7 @@
     <t>■</t>
   </si>
   <si>
-    <t>Tr:D1</t>
+    <t>Tr:D3</t>
   </si>
   <si>
     <t>DrS</t>
@@ -64,7 +64,7 @@
     <t>Mg</t>
   </si>
   <si>
-    <t>Ar:D3</t>
+    <t>Ar:D1</t>
   </si>
   <si>
     <t>Un</t>
@@ -79,10 +79,10 @@
     <t>Mv</t>
   </si>
   <si>
-    <t>Ar:D1</t>
+    <t>①</t>
   </si>
   <si>
-    <t>①</t>
+    <t>Tr:D1</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -139,7 +139,53 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -153,8 +199,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -168,74 +267,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -245,38 +277,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,37 +291,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -333,91 +309,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,13 +333,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,19 +471,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,17 +482,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -515,7 +504,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -552,9 +541,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -577,8 +568,17 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,7 +590,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -599,136 +599,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -808,19 +808,17 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
+      <sheetName val="StageEvents"/>
+      <sheetName val="Tutorials"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
@@ -1035,6 +1033,8 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4036,7 +4036,7 @@
         <v>10</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
@@ -4316,13 +4316,13 @@
         <v>10</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>10</v>
@@ -4389,13 +4389,13 @@
         <v>10</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>10</v>
@@ -4462,13 +4462,13 @@
         <v>10</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>10</v>
@@ -4588,7 +4588,7 @@
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
